--- a/gasstation/итоги.xlsx
+++ b/gasstation/итоги.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anton\education\6 семестр\модел\gasstation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89040E23-604C-4A40-8258-AB44AF87F018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A384C35B-1C16-48AF-9F42-A12FCF068EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B953F382-C8A8-40D6-83BC-37BBBE37FA30}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{B953F382-C8A8-40D6-83BC-37BBBE37FA30}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
+    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="308">
   <si>
     <t>Места в очереди</t>
   </si>
@@ -776,6 +778,252 @@
       <t xml:space="preserve"> → число потерянных клиентов значительно уменьшилось.</t>
     </r>
   </si>
+  <si>
+    <t>Группа источников риска</t>
+  </si>
+  <si>
+    <t>События риска</t>
+  </si>
+  <si>
+    <t>Признак наступления риска</t>
+  </si>
+  <si>
+    <t>Оценка вероятности</t>
+  </si>
+  <si>
+    <t>Оценка влияния на проект</t>
+  </si>
+  <si>
+    <t>Оценка риска</t>
+  </si>
+  <si>
+    <t>1. Отношения с заказчиком</t>
+  </si>
+  <si>
+    <t>1.1 Неточное определение рамок проекта</t>
+  </si>
+  <si>
+    <t>Нарастающее отставание от графика. Появление внеплановых работ. Нарастающее превышение бюджета.</t>
+  </si>
+  <si>
+    <t>Средняя</t>
+  </si>
+  <si>
+    <t>Высокое</t>
+  </si>
+  <si>
+    <t>Высокая</t>
+  </si>
+  <si>
+    <t>1.2 Изменение требований заказчика</t>
+  </si>
+  <si>
+    <t>Появление дополнительных работ. Запросы заказчика.</t>
+  </si>
+  <si>
+    <t>Очень высокая</t>
+  </si>
+  <si>
+    <t>1.3 Недоразумения в ходе выполнения проекта</t>
+  </si>
+  <si>
+    <t>Жалобы на качество и сроки исполнения проекта.</t>
+  </si>
+  <si>
+    <t>Среднее</t>
+  </si>
+  <si>
+    <t>1.4 Подготовка объекта к началу работ</t>
+  </si>
+  <si>
+    <t>Опоздание с началом работ.</t>
+  </si>
+  <si>
+    <t>2. Неопределённость в оценках проекта</t>
+  </si>
+  <si>
+    <t>2.1 Выявление дополнительных работ</t>
+  </si>
+  <si>
+    <t>Появление дополнительных работ. Срыв сроков. Превышение бюджета.</t>
+  </si>
+  <si>
+    <t>Низкая</t>
+  </si>
+  <si>
+    <t>2.2 Колебание рыночных цен</t>
+  </si>
+  <si>
+    <t>Дополнительные затраты на оборудование и ПО.</t>
+  </si>
+  <si>
+    <t>3. Команда и ресурсы проекта</t>
+  </si>
+  <si>
+    <t>3.1 Низкое качество выполнения работ</t>
+  </si>
+  <si>
+    <t>Жалобы заказчика. Срыв сроков. Дополнительные затраты.</t>
+  </si>
+  <si>
+    <t>3.2 Низкая дисциплина</t>
+  </si>
+  <si>
+    <t>Срыв сроков выполнения работ. Нарушение качества.</t>
+  </si>
+  <si>
+    <t>Очень низкая</t>
+  </si>
+  <si>
+    <t>3.3 Уход ключевых специалистов</t>
+  </si>
+  <si>
+    <t>Срыв сроков выполнения работ. Отсутствие ключевых специалистов.</t>
+  </si>
+  <si>
+    <t>4. Технические риски</t>
+  </si>
+  <si>
+    <t>4.1 Проблемы интеграции системы с сенсорами</t>
+  </si>
+  <si>
+    <t>Ошибки в передаче данных. Несовместимость оборудования.</t>
+  </si>
+  <si>
+    <t>4.2 Ошибки в алгоритмах управления</t>
+  </si>
+  <si>
+    <t>Некорректная работа системы. Повышенное энергопотребление.</t>
+  </si>
+  <si>
+    <t>5. Операционные риски</t>
+  </si>
+  <si>
+    <t>5.1 Сбой в работе аппаратной части</t>
+  </si>
+  <si>
+    <t>Полный или частичный отказ системы. Требуется замена оборудования.</t>
+  </si>
+  <si>
+    <t>5.2 Нарушение сроков поставок оборудования</t>
+  </si>
+  <si>
+    <t>Оборудование не поступило вовремя, задержка сборки прототипа.</t>
+  </si>
+  <si>
+    <t>6. Внедрение и эксплуатация</t>
+  </si>
+  <si>
+    <t>6.1 Сопротивление пользователей изменениям</t>
+  </si>
+  <si>
+    <t>Низкая вовлеченность в обучение. Негативные отзывы.</t>
+  </si>
+  <si>
+    <t>6.2 Ошибки при настройке и вводе в эксплуатацию</t>
+  </si>
+  <si>
+    <t>Некорректная работа системы после установки.</t>
+  </si>
+  <si>
+    <t>Меры реагирования</t>
+  </si>
+  <si>
+    <t>Разработка и утверждение устава проекта с четким определением границ.</t>
+  </si>
+  <si>
+    <t>Закрепление в контракте процедуры пересмотра требований с учетом сроков и бюджета.</t>
+  </si>
+  <si>
+    <t>Регулярные встречи с заказчиком, прозрачная отчетность.</t>
+  </si>
+  <si>
+    <t>Закрепление обязательств заказчика по подготовке объекта перед началом работ.</t>
+  </si>
+  <si>
+    <t>Включение резерва времени и бюджета, формализация процесса согласования дополнительных работ.</t>
+  </si>
+  <si>
+    <t>Заключение контрактов с фиксированной ценой или предусмотрение индексации.</t>
+  </si>
+  <si>
+    <t>Введение системы контроля качества, регулярные проверки.</t>
+  </si>
+  <si>
+    <t>Внедрение системы мотивации, четкие KPI.</t>
+  </si>
+  <si>
+    <t>Создание базы знаний, документация всех ключевых процессов.</t>
+  </si>
+  <si>
+    <t>Проведение тестирования совместимости оборудования на ранних этапах.</t>
+  </si>
+  <si>
+    <t>Разработка прототипов, поэтапное тестирование алгоритмов.</t>
+  </si>
+  <si>
+    <t>Закладка резервных ресурсов, оперативная техническая поддержка.</t>
+  </si>
+  <si>
+    <t>Работа с несколькими поставщиками, закупка критичных компонентов заранее.</t>
+  </si>
+  <si>
+    <t>Проведение обучающих программ, демонстрация преимуществ системы.</t>
+  </si>
+  <si>
+    <t>Многоступенчатое тестирование перед запуском, детальная документация.</t>
+  </si>
+  <si>
+    <t>Switch №</t>
+  </si>
+  <si>
+    <t>BID</t>
+  </si>
+  <si>
+    <t>PID</t>
+  </si>
+  <si>
+    <t>Стоимость порта</t>
+  </si>
+  <si>
+    <t>RPC</t>
+  </si>
+  <si>
+    <t>Приоритет моста</t>
+  </si>
+  <si>
+    <t>МАС моста</t>
+  </si>
+  <si>
+    <t>Приоритет порта</t>
+  </si>
+  <si>
+    <t>Номер порта</t>
+  </si>
+  <si>
+    <t>6      Root</t>
+  </si>
+  <si>
+    <t>1C:B5:53:8C:01:50</t>
+  </si>
+  <si>
+    <t>1C:B5:53:8C:01:51</t>
+  </si>
+  <si>
+    <t>0+2=2</t>
+  </si>
+  <si>
+    <t>1C:B5:53:8C:01:52</t>
+  </si>
+  <si>
+    <t>2+4=6</t>
+  </si>
+  <si>
+    <t>1C:B5:53:8C:01:53</t>
+  </si>
+  <si>
+    <t>0+4=4</t>
+  </si>
 </sst>
 </file>
 
@@ -784,7 +1032,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -809,16 +1057,62 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4C6E7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF7D7D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBDBDB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -981,11 +1275,342 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1063,6 +1688,132 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -4416,4 +5167,776 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D001B0C2-4A4D-431A-8C0C-16DB39E3151B}">
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="3" width="26" customWidth="1"/>
+    <col min="4" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" customWidth="1"/>
+    <col min="11" max="13" width="20.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+    </row>
+    <row r="2" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="31" t="s">
+        <v>232</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32"/>
+      <c r="B3" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>239</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="K3" s="6"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="32"/>
+      <c r="B4" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="K4" s="6"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="32"/>
+      <c r="B5" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="K5" s="6"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="31" t="s">
+        <v>246</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>247</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="6"/>
+    </row>
+    <row r="7" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="32"/>
+      <c r="B7" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="K7" s="6"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="31" t="s">
+        <v>252</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="6"/>
+    </row>
+    <row r="9" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="32"/>
+      <c r="B9" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="K9" s="6"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="6"/>
+    </row>
+    <row r="10" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="32"/>
+      <c r="B10" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>259</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="G10" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="K10" s="6"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="6"/>
+    </row>
+    <row r="11" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="31" t="s">
+        <v>260</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="G11" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="6"/>
+    </row>
+    <row r="12" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="32"/>
+      <c r="B12" s="31" t="s">
+        <v>263</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="K12" s="6"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="6"/>
+    </row>
+    <row r="13" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
+        <v>265</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>266</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>287</v>
+      </c>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="6"/>
+    </row>
+    <row r="14" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="32"/>
+      <c r="B14" s="31" t="s">
+        <v>268</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="E14" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>288</v>
+      </c>
+      <c r="K14" s="6"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="6"/>
+    </row>
+    <row r="15" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>271</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>289</v>
+      </c>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="6"/>
+    </row>
+    <row r="16" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="32"/>
+      <c r="B16" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="E16" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="K16" s="6"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18BF3D88-B717-4890-94D1-1DEE25C51264}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="B1" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1" s="51"/>
+      <c r="D1" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="E1" s="51"/>
+      <c r="F1" s="47" t="s">
+        <v>294</v>
+      </c>
+      <c r="G1" s="47" t="s">
+        <v>295</v>
+      </c>
+      <c r="H1" s="6"/>
+    </row>
+    <row r="2" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="48"/>
+      <c r="B2" s="52" t="s">
+        <v>296</v>
+      </c>
+      <c r="C2" s="54" t="s">
+        <v>297</v>
+      </c>
+      <c r="D2" s="52" t="s">
+        <v>298</v>
+      </c>
+      <c r="E2" s="54" t="s">
+        <v>299</v>
+      </c>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="49"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="56" t="s">
+        <v>300</v>
+      </c>
+      <c r="B4" s="33">
+        <v>32768</v>
+      </c>
+      <c r="C4" s="57" t="s">
+        <v>301</v>
+      </c>
+      <c r="D4" s="36">
+        <v>128</v>
+      </c>
+      <c r="E4" s="37">
+        <v>4</v>
+      </c>
+      <c r="F4" s="38">
+        <v>4</v>
+      </c>
+      <c r="G4" s="38">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="48"/>
+      <c r="B5" s="33">
+        <v>-4097</v>
+      </c>
+      <c r="C5" s="58"/>
+      <c r="D5" s="36">
+        <v>128</v>
+      </c>
+      <c r="E5" s="37">
+        <v>5</v>
+      </c>
+      <c r="F5" s="38">
+        <v>2</v>
+      </c>
+      <c r="G5" s="38">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="48"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="36">
+        <v>128</v>
+      </c>
+      <c r="E6" s="37">
+        <v>6</v>
+      </c>
+      <c r="F6" s="38">
+        <v>2</v>
+      </c>
+      <c r="G6" s="38">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+    </row>
+    <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="48"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="36">
+        <v>128</v>
+      </c>
+      <c r="E7" s="37">
+        <v>7</v>
+      </c>
+      <c r="F7" s="38">
+        <v>2</v>
+      </c>
+      <c r="G7" s="38">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="49"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="39">
+        <v>128</v>
+      </c>
+      <c r="E8" s="40">
+        <v>8</v>
+      </c>
+      <c r="F8" s="41">
+        <v>2</v>
+      </c>
+      <c r="G8" s="41">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="56">
+        <v>3</v>
+      </c>
+      <c r="B9" s="33">
+        <v>32769</v>
+      </c>
+      <c r="C9" s="57" t="s">
+        <v>302</v>
+      </c>
+      <c r="D9" s="52">
+        <v>128</v>
+      </c>
+      <c r="E9" s="69">
+        <v>4</v>
+      </c>
+      <c r="F9" s="60">
+        <v>2</v>
+      </c>
+      <c r="G9" s="60" t="s">
+        <v>303</v>
+      </c>
+      <c r="H9" s="63"/>
+      <c r="I9" s="62"/>
+    </row>
+    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="49"/>
+      <c r="B10" s="42">
+        <v>-8193</v>
+      </c>
+      <c r="C10" s="55"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="62"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="56">
+        <v>4</v>
+      </c>
+      <c r="B11" s="33">
+        <v>32770</v>
+      </c>
+      <c r="C11" s="57" t="s">
+        <v>304</v>
+      </c>
+      <c r="D11" s="36">
+        <v>128</v>
+      </c>
+      <c r="E11" s="44">
+        <v>1</v>
+      </c>
+      <c r="F11" s="38">
+        <v>2</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+    </row>
+    <row r="12" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="48"/>
+      <c r="B12" s="33">
+        <v>-12289</v>
+      </c>
+      <c r="C12" s="58"/>
+      <c r="D12" s="36">
+        <v>128</v>
+      </c>
+      <c r="E12" s="68">
+        <v>2</v>
+      </c>
+      <c r="F12" s="38">
+        <v>4</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>305</v>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+    </row>
+    <row r="13" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="48"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="6"/>
+    </row>
+    <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="64"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="6"/>
+    </row>
+    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="66">
+        <v>5</v>
+      </c>
+      <c r="B15" s="33">
+        <v>32771</v>
+      </c>
+      <c r="C15" s="67" t="s">
+        <v>306</v>
+      </c>
+      <c r="D15" s="36">
+        <v>128</v>
+      </c>
+      <c r="E15" s="46">
+        <v>4</v>
+      </c>
+      <c r="F15" s="38">
+        <v>4</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>305</v>
+      </c>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+    </row>
+    <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="48"/>
+      <c r="B16" s="33">
+        <v>-16385</v>
+      </c>
+      <c r="C16" s="58"/>
+      <c r="D16" s="36">
+        <v>128</v>
+      </c>
+      <c r="E16" s="44">
+        <v>7</v>
+      </c>
+      <c r="F16" s="38">
+        <v>2</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+    </row>
+    <row r="17" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="64"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="36">
+        <v>128</v>
+      </c>
+      <c r="E17" s="46">
+        <v>8</v>
+      </c>
+      <c r="F17" s="38">
+        <v>4</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>307</v>
+      </c>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="G1:G3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/gasstation/итоги.xlsx
+++ b/gasstation/итоги.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anton\education\6 семестр\модел\gasstation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A384C35B-1C16-48AF-9F42-A12FCF068EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3126C76-3A1C-4567-80B3-75FD1583A866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{B953F382-C8A8-40D6-83BC-37BBBE37FA30}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{B953F382-C8A8-40D6-83BC-37BBBE37FA30}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
-    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
+    <sheet name="Лист4" sheetId="4" r:id="rId2"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId3"/>
+    <sheet name="Лист3" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="345">
   <si>
     <t>Места в очереди</t>
   </si>
@@ -218,9 +219,6 @@
     <t>Хорошо при стабильном потоке клиентов</t>
   </si>
   <si>
-    <t>Вероятность 1 заявки в очереди</t>
-  </si>
-  <si>
     <t>Нет необходимости ожидания</t>
   </si>
   <si>
@@ -233,9 +231,6 @@
     <t>Не требуется изменение системы</t>
   </si>
   <si>
-    <t>Вероятность 3 заявок в очереди</t>
-  </si>
-  <si>
     <t>Система справляется с нагрузкой</t>
   </si>
   <si>
@@ -264,9 +259,6 @@
   </si>
   <si>
     <t>Удерживать или снижать показатель</t>
-  </si>
-  <si>
-    <t>Среднее время нахождения заявок в очереди</t>
   </si>
   <si>
     <t>Клиенты быстро проходят процесс</t>
@@ -1023,6 +1015,133 @@
   </si>
   <si>
     <t>0+4=4</t>
+  </si>
+  <si>
+    <t>Выгода владельца</t>
+  </si>
+  <si>
+    <t>Выгода клиента</t>
+  </si>
+  <si>
+    <t>Выше доход, если выше вероятность обслуживания</t>
+  </si>
+  <si>
+    <t>Чем выше вероятность, тем меньше отказов</t>
+  </si>
+  <si>
+    <t>Больше заявок — выше прибыль</t>
+  </si>
+  <si>
+    <t>Быстрее проходит обслуживание</t>
+  </si>
+  <si>
+    <t>Потеря прибыли из-за отказов</t>
+  </si>
+  <si>
+    <t>Риск остаться без обслуживания</t>
+  </si>
+  <si>
+    <t>Низкая загрузка — потеря ресурса</t>
+  </si>
+  <si>
+    <t>Меньше очереди</t>
+  </si>
+  <si>
+    <t>Высокая загрузка увеличивает прибыль</t>
+  </si>
+  <si>
+    <t>Эффективное использование мощностей</t>
+  </si>
+  <si>
+    <t>Меньше простаивающих заявок</t>
+  </si>
+  <si>
+    <t>Высокий простой — потери</t>
+  </si>
+  <si>
+    <t>Чем ниже, тем быстрее обслуживание</t>
+  </si>
+  <si>
+    <t>Аналогично первому КО</t>
+  </si>
+  <si>
+    <t>Аналогично</t>
+  </si>
+  <si>
+    <t>Низкие очереди — потери ресурсов</t>
+  </si>
+  <si>
+    <t>Клиенты сразу получают услугу</t>
+  </si>
+  <si>
+    <t>Стабильная нагрузка</t>
+  </si>
+  <si>
+    <t>Ожидание в пределах нормы</t>
+  </si>
+  <si>
+    <t>Возможность роста прибыли</t>
+  </si>
+  <si>
+    <t>Риск долгого ожидания</t>
+  </si>
+  <si>
+    <t>Очередь загружена, но без отказов</t>
+  </si>
+  <si>
+    <t>Долгое ожидание</t>
+  </si>
+  <si>
+    <t>Умеренная очередь — высокая эффективность</t>
+  </si>
+  <si>
+    <t>Чем меньше, тем лучше</t>
+  </si>
+  <si>
+    <t>Меньше времени в очереди — выше throughput</t>
+  </si>
+  <si>
+    <t>Клиенты тратят меньше времени</t>
+  </si>
+  <si>
+    <t>Быстрее обслуживание — выше доход</t>
+  </si>
+  <si>
+    <t>Чем меньше время, тем удобнее</t>
+  </si>
+  <si>
+    <t>Чем меньше, тем быстрее поток заявок</t>
+  </si>
+  <si>
+    <t>Клиент тратит меньше времени</t>
+  </si>
+  <si>
+    <t>Оптимально при умеренных значениях</t>
+  </si>
+  <si>
+    <t>Высокие значения — долгие очереди</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оптимальным количеством мест в очереди является 3МО, так как система показывает наилучшие показатели при допустимых потерях.
+Максимальная вероятность обслуживания – 82,1%, что означает, что большинство клиентов получат услугу без отказов.
+Пропускная способность достигает 9,002 заявки/час, что является наибольшим значением среди всех вариантов, увеличивая доход владельца.
+Вероятность отказа минимальна – всего 19,4%, что означает, что лишь небольшая часть клиентов останется без обслуживания.
+Очереди присутствуют, но управляемы – среднее количество заявок в очереди 1,391, вероятность наличия 3 заявок в очереди 22,5%, но это допустимо, так как клиенты все равно обслуживаются.
+Среднее время ожидания остается в приемлемых пределах (0,067 единиц времени), а время нахождения заявки в системе лишь немного больше, чем при 2МО.
+Таким образом, 3МО – наилучший баланс между высокой пропускной способностью, максимизацией прибыли и сохранением удовлетворенности клиентов.
+</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>медианное</t>
+  </si>
+  <si>
+    <t>средняя</t>
+  </si>
+  <si>
+    <t>мода</t>
   </si>
 </sst>
 </file>
@@ -1112,7 +1231,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -1606,11 +1725,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1670,10 +1798,6 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1742,6 +1866,24 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1769,7 +1911,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1778,7 +1926,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1787,32 +1950,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1829,6 +1968,1010 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:areaChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>теория</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Лист4!$B$1:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист4!$H$1:$H$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.30000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.79999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.89999999999999991</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.99999999999999989</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8FB0-43AD-B834-C5C3EF96A2AC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>практика</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Лист4!$B$1:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист4!$G$1:$G$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.15000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8FB0-43AD-B834-C5C3EF96A2AC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1730285247"/>
+        <c:axId val="1730286687"/>
+      </c:areaChart>
+      <c:catAx>
+        <c:axId val="1730285247"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1730286687"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:tickLblSkip val="1"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1730286687"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1730285247"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="276">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40C79EA8-2BB0-3448-1E69-E31D6343CB2E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2128,14 +3271,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{691F121E-7A5D-4BB1-AEF6-E7DE22AC7A8C}">
-  <dimension ref="A1:M117"/>
+  <dimension ref="A1:P117"/>
   <sheetFormatPr defaultColWidth="18.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="24" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2145,7 +3288,7 @@
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2162,7 +3305,7 @@
       <c r="H2" s="9"/>
       <c r="I2" s="10"/>
     </row>
-    <row r="3" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
         <v>5</v>
       </c>
@@ -2175,17 +3318,24 @@
       <c r="D3" s="14"/>
       <c r="E3" s="15"/>
       <c r="F3" s="16"/>
-      <c r="G3" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>9</v>
+      <c r="G3" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>306</v>
       </c>
       <c r="I3" s="18" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+    </row>
+    <row r="4" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19">
         <v>1</v>
       </c>
@@ -2204,11 +3354,22 @@
       <c r="F4" s="21">
         <v>0.82099999999999995</v>
       </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="23"/>
+      <c r="G4" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>308</v>
+      </c>
       <c r="I4" s="10"/>
-    </row>
-    <row r="5" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J4" s="27"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+    </row>
+    <row r="5" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="19">
         <v>2</v>
       </c>
@@ -2227,11 +3388,22 @@
       <c r="F5" s="21">
         <v>9.0020000000000007</v>
       </c>
-      <c r="G5" s="22"/>
-      <c r="H5" s="23"/>
+      <c r="G5" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>310</v>
+      </c>
       <c r="I5" s="10"/>
-    </row>
-    <row r="6" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J5" s="27"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+    </row>
+    <row r="6" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19">
         <v>3</v>
       </c>
@@ -2250,15 +3422,26 @@
       <c r="F6" s="21">
         <v>0.19400000000000001</v>
       </c>
-      <c r="G6" s="22"/>
-      <c r="H6" s="23"/>
+      <c r="G6" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>312</v>
+      </c>
       <c r="I6" s="10"/>
-    </row>
-    <row r="7" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J6" s="27"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+    </row>
+    <row r="7" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="19">
         <v>4</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="21">
@@ -2273,15 +3456,26 @@
       <c r="F7" s="21">
         <v>0.109410801963993</v>
       </c>
-      <c r="G7" s="22"/>
-      <c r="H7" s="23"/>
+      <c r="G7" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>314</v>
+      </c>
       <c r="I7" s="10"/>
-    </row>
-    <row r="8" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J7" s="27"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+    </row>
+    <row r="8" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="19">
         <v>5</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="21">
@@ -2296,11 +3490,22 @@
       <c r="F8" s="21">
         <v>0.87283142389525303</v>
       </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="23"/>
+      <c r="G8" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>170</v>
+      </c>
       <c r="I8" s="10"/>
-    </row>
-    <row r="9" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J8" s="27"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+    </row>
+    <row r="9" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="19">
         <v>6</v>
       </c>
@@ -2319,15 +3524,26 @@
       <c r="F9" s="21">
         <v>1.8550736497545</v>
       </c>
-      <c r="G9" s="22"/>
-      <c r="H9" s="23"/>
+      <c r="G9" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>317</v>
+      </c>
       <c r="I9" s="10"/>
-    </row>
-    <row r="10" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J9" s="27"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+    </row>
+    <row r="10" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="19">
         <v>7</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="22" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="21">
@@ -2342,15 +3558,26 @@
       <c r="F10" s="21">
         <v>6.1211129296235497E-2</v>
       </c>
-      <c r="G10" s="22"/>
-      <c r="H10" s="23"/>
+      <c r="G10" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>319</v>
+      </c>
       <c r="I10" s="10"/>
-    </row>
-    <row r="11" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J10" s="27"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+    </row>
+    <row r="11" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="19">
         <v>8</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="22" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="21">
@@ -2365,15 +3592,26 @@
       <c r="F11" s="21">
         <v>8.3715220949263397E-2</v>
       </c>
-      <c r="G11" s="22"/>
-      <c r="H11" s="23"/>
+      <c r="G11" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="I11" s="10"/>
-    </row>
-    <row r="12" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J11" s="27"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+    </row>
+    <row r="12" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="19">
         <v>9</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="22" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="21">
@@ -2388,15 +3626,22 @@
       <c r="F12" s="21">
         <v>8.3715220949263397E-2</v>
       </c>
-      <c r="G12" s="22"/>
-      <c r="H12" s="23"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
       <c r="I12" s="10"/>
-    </row>
-    <row r="13" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J12" s="27"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+    </row>
+    <row r="13" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="19">
         <v>10</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="22" t="s">
         <v>20</v>
       </c>
       <c r="C13" s="21">
@@ -2411,15 +3656,26 @@
       <c r="F13" s="21">
         <v>0.30808002481389501</v>
       </c>
-      <c r="G13" s="22"/>
-      <c r="H13" s="23"/>
+      <c r="G13" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>323</v>
+      </c>
       <c r="I13" s="10"/>
-    </row>
-    <row r="14" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J13" s="27"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+    </row>
+    <row r="14" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="19">
         <v>11</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="22" t="s">
         <v>21</v>
       </c>
       <c r="C14" s="21">
@@ -2434,11 +3690,22 @@
       <c r="F14" s="21">
         <v>0.21789702233250599</v>
       </c>
-      <c r="G14" s="22"/>
-      <c r="H14" s="23"/>
+      <c r="G14" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>325</v>
+      </c>
       <c r="I14" s="10"/>
-    </row>
-    <row r="15" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J14" s="27"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+    </row>
+    <row r="15" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="19">
         <v>12</v>
       </c>
@@ -2457,15 +3724,26 @@
       <c r="F15" s="21">
         <v>0.249379652605459</v>
       </c>
-      <c r="G15" s="22"/>
-      <c r="H15" s="23"/>
+      <c r="G15" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>327</v>
+      </c>
       <c r="I15" s="10"/>
-    </row>
-    <row r="16" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J15" s="27"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+    </row>
+    <row r="16" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="19">
         <v>13</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="23" t="s">
         <v>23</v>
       </c>
       <c r="C16" s="21">
@@ -2480,11 +3758,22 @@
       <c r="F16" s="21">
         <v>0.224643300248138</v>
       </c>
-      <c r="G16" s="22"/>
-      <c r="H16" s="23"/>
+      <c r="G16" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>329</v>
+      </c>
       <c r="I16" s="10"/>
-    </row>
-    <row r="17" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J16" s="27"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+    </row>
+    <row r="17" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="19">
         <v>14</v>
       </c>
@@ -2503,15 +3792,26 @@
       <c r="F17" s="21">
         <v>1.3905862282878401</v>
       </c>
-      <c r="G17" s="22"/>
-      <c r="H17" s="23"/>
+      <c r="G17" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>331</v>
+      </c>
       <c r="I17" s="10"/>
-    </row>
-    <row r="18" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J17" s="27"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+    </row>
+    <row r="18" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="19">
         <v>15</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="24" t="s">
         <v>25</v>
       </c>
       <c r="C18" s="21">
@@ -2526,11 +3826,22 @@
       <c r="F18" s="21">
         <v>6.6589552238805902E-2</v>
       </c>
-      <c r="G18" s="22"/>
-      <c r="H18" s="23"/>
+      <c r="G18" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>333</v>
+      </c>
       <c r="I18" s="10"/>
-    </row>
-    <row r="19" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J18" s="27"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+    </row>
+    <row r="19" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="19">
         <v>16</v>
       </c>
@@ -2549,15 +3860,26 @@
       <c r="F19" s="21">
         <v>0.109118181818181</v>
       </c>
-      <c r="G19" s="22"/>
-      <c r="H19" s="10"/>
+      <c r="G19" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>335</v>
+      </c>
       <c r="I19" s="10"/>
-    </row>
-    <row r="20" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J19" s="27"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+    </row>
+    <row r="20" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="19">
         <v>17</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="24" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="21">
@@ -2572,11 +3894,22 @@
       <c r="F20" s="21">
         <v>0.175707734056987</v>
       </c>
-      <c r="G20" s="22"/>
-      <c r="H20" s="10"/>
+      <c r="G20" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>337</v>
+      </c>
       <c r="I20" s="10"/>
-    </row>
-    <row r="21" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J20" s="27"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+    </row>
+    <row r="21" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="15">
         <v>18</v>
       </c>
@@ -2595,13 +3928,36 @@
       <c r="F21" s="21">
         <v>3.2820512820512802</v>
       </c>
-      <c r="G21" s="22"/>
-      <c r="H21" s="10"/>
+      <c r="G21" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>339</v>
+      </c>
       <c r="I21" s="10"/>
-    </row>
-    <row r="22" spans="1:12" ht="36.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J21" s="27"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+    </row>
+    <row r="22" spans="1:16" ht="162.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="49" t="s">
+        <v>340</v>
+      </c>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+    </row>
+    <row r="23" spans="1:16" ht="184.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+    </row>
+    <row r="24" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C24" s="3" t="s">
         <v>0</v>
       </c>
@@ -2613,7 +3969,7 @@
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
     </row>
-    <row r="25" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C25" s="7" t="s">
         <v>1</v>
       </c>
@@ -2623,7 +3979,7 @@
       <c r="E25" s="9"/>
       <c r="F25" s="10"/>
     </row>
-    <row r="26" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
         <v>5</v>
       </c>
@@ -2633,614 +3989,494 @@
       <c r="C26" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="F26" s="18" t="s">
+      <c r="F26" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="G26" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="H26" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="I26" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="J26" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="K26" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="L26" s="27" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+    </row>
+    <row r="27" spans="1:16" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="19">
         <v>1</v>
       </c>
       <c r="B27" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="21">
+      <c r="C27" s="46">
         <v>0.49299999999999999</v>
       </c>
-      <c r="D27" s="22"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="6">
-        <v>1</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I27" s="6">
-        <v>0.49299999999999999</v>
-      </c>
-      <c r="J27" s="6" t="s">
+      <c r="D27" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="K27" s="6" t="s">
+      <c r="E27" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="L27" s="6" t="s">
+      <c r="F27" s="30" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
+    </row>
+    <row r="28" spans="1:16" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="19">
         <v>2</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="21">
+      <c r="C28" s="46">
         <v>5.5640000000000001</v>
       </c>
-      <c r="D28" s="22"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="6">
-        <v>2</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I28" s="6">
-        <v>5.5640000000000001</v>
-      </c>
-      <c r="J28" s="6" t="s">
+      <c r="D28" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="K28" s="6" t="s">
+      <c r="E28" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="L28" s="6" t="s">
+      <c r="F28" s="30" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+    </row>
+    <row r="29" spans="1:16" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="19">
         <v>3</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="21">
+      <c r="C29" s="46">
         <v>0.50700000000000001</v>
       </c>
-      <c r="D29" s="22"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="6">
-        <v>3</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I29" s="6">
-        <v>0.50700000000000001</v>
-      </c>
-      <c r="J29" s="6" t="s">
+      <c r="D29" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="E29" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="L29" s="6" t="s">
+      <c r="F29" s="30" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+    </row>
+    <row r="30" spans="1:16" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="19">
         <v>4</v>
       </c>
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="21">
+      <c r="C30" s="46">
         <v>0.35842535614937099</v>
       </c>
-      <c r="D30" s="22"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="6">
-        <v>4</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I30" s="6">
-        <v>0.35799999999999998</v>
-      </c>
-      <c r="J30" s="6" t="s">
+      <c r="D30" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="K30" s="6" t="s">
+      <c r="E30" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="L30" s="6" t="s">
+      <c r="F30" s="30" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+    </row>
+    <row r="31" spans="1:16" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="19">
         <v>5</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="B31" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="21">
+      <c r="C31" s="46">
         <v>0.55685745595549196</v>
       </c>
-      <c r="D31" s="22"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="6">
-        <v>5</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" s="6">
-        <v>0.55700000000000005</v>
-      </c>
-      <c r="J31" s="6" t="s">
+      <c r="D31" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="K31" s="6" t="s">
+      <c r="E31" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="L31" s="6" t="s">
+      <c r="F31" s="30" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+    </row>
+    <row r="32" spans="1:16" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="19">
         <v>6</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="21">
+      <c r="C32" s="46">
         <v>1.4721402680603499</v>
       </c>
-      <c r="D32" s="22"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="6">
-        <v>6</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I32" s="6">
-        <v>1.472</v>
-      </c>
-      <c r="J32" s="6" t="s">
+      <c r="D32" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="K32" s="6" t="s">
+      <c r="E32" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="L32" s="6" t="s">
+      <c r="F32" s="30" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+    </row>
+    <row r="33" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="19">
         <v>7</v>
       </c>
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="21">
+      <c r="C33" s="46">
         <v>0.32597150805024</v>
       </c>
-      <c r="D33" s="22"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="6">
-        <v>7</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I33" s="6">
-        <v>0.32600000000000001</v>
-      </c>
-      <c r="J33" s="6" t="s">
+      <c r="D33" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="K33" s="6" t="s">
+      <c r="E33" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="L33" s="6" t="s">
+      <c r="F33" s="30" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+    </row>
+    <row r="34" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="19">
         <v>8</v>
       </c>
-      <c r="B34" s="24" t="s">
+      <c r="B34" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="21">
+      <c r="C34" s="46">
         <v>0.201888223889404</v>
       </c>
-      <c r="D34" s="22"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="6">
-        <v>8</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I34" s="6">
-        <v>0.20200000000000001</v>
-      </c>
-      <c r="J34" s="6" t="s">
+      <c r="D34" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="K34" s="6" t="s">
+      <c r="E34" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="L34" s="6" t="s">
+      <c r="F34" s="30" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+    </row>
+    <row r="35" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="19">
         <v>9</v>
       </c>
-      <c r="B35" s="24" t="s">
+      <c r="B35" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C35" s="21">
+      <c r="C35" s="46">
         <v>0.201888223889404</v>
       </c>
-      <c r="D35" s="22"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="6">
-        <v>9</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I35" s="6">
-        <v>0.20200000000000001</v>
-      </c>
-      <c r="J35" s="6" t="s">
+      <c r="D35" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="K35" s="6" t="s">
+      <c r="E35" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="L35" s="6" t="s">
+      <c r="F35" s="30" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+    </row>
+    <row r="36" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="19">
         <v>10</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="B36" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="21">
+      <c r="C36" s="46">
         <v>1</v>
       </c>
-      <c r="D36" s="22"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="6">
-        <v>10</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I36" s="6">
-        <v>1</v>
-      </c>
-      <c r="J36" s="6" t="s">
+      <c r="D36" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="K36" s="6" t="s">
+      <c r="E36" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="6" t="s">
+      <c r="F36" s="30" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+    </row>
+    <row r="37" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="19">
         <v>11</v>
       </c>
-      <c r="B37" s="24" t="s">
+      <c r="B37" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="21">
+      <c r="C37" s="46">
         <v>0</v>
       </c>
-      <c r="D37" s="22"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="6">
-        <v>11</v>
-      </c>
-      <c r="H37" s="6" t="s">
+      <c r="D37" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="E37" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="I37" s="6">
-        <v>0</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K37" s="6" t="s">
+      <c r="F37" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="L37" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+    </row>
+    <row r="38" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="19">
         <v>12</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="21">
+      <c r="C38" s="46">
         <v>0</v>
       </c>
-      <c r="D38" s="22"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="6">
-        <v>12</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I38" s="6">
-        <v>0</v>
-      </c>
-      <c r="J38" s="6" t="s">
+      <c r="D38" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="K38" s="6" t="s">
+      <c r="E38" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="F38" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="L38" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+    </row>
+    <row r="39" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="19">
         <v>13</v>
       </c>
-      <c r="B39" s="25" t="s">
+      <c r="B39" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="21">
+      <c r="C39" s="46">
         <v>0</v>
       </c>
-      <c r="D39" s="22"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="6">
-        <v>13</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="I39" s="6">
-        <v>0</v>
-      </c>
-      <c r="J39" s="6" t="s">
+      <c r="D39" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="K39" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="L39" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E39" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="F39" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+    </row>
+    <row r="40" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="19">
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="21">
+      <c r="C40" s="46">
         <v>0</v>
       </c>
-      <c r="D40" s="22"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="6">
-        <v>14</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I40" s="6">
-        <v>0</v>
-      </c>
-      <c r="J40" s="6" t="s">
+      <c r="D40" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E40" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="F40" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="K40" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="L40" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
+    </row>
+    <row r="41" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="19">
         <v>15</v>
       </c>
-      <c r="B41" s="26" t="s">
+      <c r="B41" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C41" s="21">
+      <c r="C41" s="46">
         <v>0</v>
       </c>
-      <c r="D41" s="22"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="6">
-        <v>15</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I41" s="6">
-        <v>0</v>
-      </c>
-      <c r="J41" s="6" t="s">
+      <c r="D41" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="E41" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="F41" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="K41" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="L41" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+    </row>
+    <row r="42" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="19">
         <v>16</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C42" s="21">
+      <c r="C42" s="46">
         <v>0.16205970149253701</v>
       </c>
-      <c r="D42" s="22"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="6">
-        <v>16</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I42" s="6">
-        <v>0.16200000000000001</v>
-      </c>
-      <c r="J42" s="6" t="s">
+      <c r="D42" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="E42" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F42" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="K42" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+    </row>
+    <row r="43" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="19">
         <v>17</v>
       </c>
-      <c r="B43" s="26" t="s">
+      <c r="B43" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="C43" s="21">
+      <c r="C43" s="46">
         <v>0.16205970149253701</v>
       </c>
-      <c r="D43" s="22"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="6">
-        <v>17</v>
-      </c>
-      <c r="H43" s="6" t="s">
+      <c r="D43" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="E43" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F43" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="I43" s="6">
-        <v>0.16200000000000001</v>
-      </c>
-      <c r="J43" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="K43" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="L43" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+    </row>
+    <row r="44" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="15">
         <v>18</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C44" s="21">
+      <c r="C44" s="46">
         <v>1.42397931945263</v>
       </c>
-      <c r="D44" s="22"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="6">
-        <v>18</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I44" s="6">
-        <v>1.4239999999999999</v>
-      </c>
-      <c r="J44" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="K44" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="L44" s="6" t="s">
-        <v>85</v>
-      </c>
+      <c r="D44" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="E44" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="F44" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
     </row>
     <row r="45" spans="1:12" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>86</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
     </row>
     <row r="46" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="47" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3284,24 +4520,8 @@
       <c r="F49" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="H49" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="I49" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="J49" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="K49" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="L49" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="M49" s="27" t="s">
-        <v>10</v>
-      </c>
+      <c r="H49" s="25"/>
+      <c r="I49" s="25"/>
     </row>
     <row r="50" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="19">
@@ -3313,26 +4533,22 @@
       <c r="C50" s="21">
         <v>0.63400000000000001</v>
       </c>
-      <c r="D50" s="22"/>
-      <c r="E50" s="23"/>
-      <c r="F50" s="10"/>
-      <c r="H50" s="6">
-        <v>1</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J50" s="6">
-        <v>0.63400000000000001</v>
-      </c>
-      <c r="K50" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="L50" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="M50" s="6" t="s">
-        <v>89</v>
+      <c r="D50" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="25"/>
+      <c r="K50" s="25"/>
+      <c r="L50" s="25"/>
+      <c r="M50" s="25" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3345,26 +4561,22 @@
       <c r="C51" s="21">
         <v>6.96</v>
       </c>
-      <c r="D51" s="22"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="10"/>
-      <c r="H51" s="6">
-        <v>2</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J51" s="6">
-        <v>6.96</v>
-      </c>
-      <c r="K51" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="L51" s="6" t="s">
-        <v>91</v>
-      </c>
+      <c r="D51" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="6"/>
       <c r="M51" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3377,90 +4589,78 @@
       <c r="C52" s="21">
         <v>0.36599999999999999</v>
       </c>
-      <c r="D52" s="22"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="10"/>
-      <c r="H52" s="6">
-        <v>3</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J52" s="6">
-        <v>0.36599999999999999</v>
-      </c>
-      <c r="K52" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="L52" s="6" t="s">
-        <v>94</v>
-      </c>
+      <c r="D52" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
       <c r="M52" s="6" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="19">
         <v>4</v>
       </c>
-      <c r="B53" s="24" t="s">
+      <c r="B53" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C53" s="21">
         <v>0.281035047494268</v>
       </c>
-      <c r="D53" s="22"/>
-      <c r="E53" s="23"/>
-      <c r="F53" s="10"/>
-      <c r="H53" s="6">
-        <v>4</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J53" s="6">
-        <v>0.28100000000000003</v>
-      </c>
-      <c r="K53" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="L53" s="6" t="s">
-        <v>97</v>
-      </c>
+      <c r="D53" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
       <c r="M53" s="6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="19">
         <v>5</v>
       </c>
-      <c r="B54" s="24" t="s">
+      <c r="B54" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C54" s="21">
         <v>0.63216508352440204</v>
       </c>
-      <c r="D54" s="22"/>
-      <c r="E54" s="23"/>
-      <c r="F54" s="10"/>
-      <c r="H54" s="6">
-        <v>5</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J54" s="6">
-        <v>0.63200000000000001</v>
-      </c>
-      <c r="K54" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="L54" s="6" t="s">
-        <v>100</v>
-      </c>
+      <c r="D54" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
       <c r="M54" s="6" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3473,186 +4673,162 @@
       <c r="C55" s="21">
         <v>1.5453652145430701</v>
       </c>
-      <c r="D55" s="22"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="10"/>
-      <c r="H55" s="6">
-        <v>6</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J55" s="6">
-        <v>1.5449999999999999</v>
-      </c>
-      <c r="K55" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="L55" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="D55" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
       <c r="M55" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="19">
         <v>7</v>
       </c>
-      <c r="B56" s="24" t="s">
+      <c r="B56" s="22" t="s">
         <v>17</v>
       </c>
       <c r="C56" s="21">
         <v>0.30306256141500099</v>
       </c>
-      <c r="D56" s="22"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="10"/>
-      <c r="H56" s="6">
-        <v>7</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J56" s="6">
-        <v>0.30299999999999999</v>
-      </c>
-      <c r="K56" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="L56" s="6" t="s">
-        <v>106</v>
-      </c>
+      <c r="D56" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
       <c r="M56" s="6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="19">
         <v>8</v>
       </c>
-      <c r="B57" s="24" t="s">
+      <c r="B57" s="22" t="s">
         <v>18</v>
       </c>
       <c r="C57" s="21">
         <v>0.151572224041925</v>
       </c>
-      <c r="D57" s="22"/>
-      <c r="E57" s="23"/>
-      <c r="F57" s="10"/>
-      <c r="H57" s="6">
-        <v>8</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J57" s="6">
-        <v>0.152</v>
-      </c>
-      <c r="K57" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="L57" s="6" t="s">
-        <v>109</v>
-      </c>
+      <c r="D57" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
       <c r="M57" s="6" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="19">
         <v>9</v>
       </c>
-      <c r="B58" s="24" t="s">
+      <c r="B58" s="22" t="s">
         <v>19</v>
       </c>
       <c r="C58" s="21">
         <v>0.151572224041925</v>
       </c>
-      <c r="D58" s="22"/>
-      <c r="E58" s="23"/>
-      <c r="F58" s="10"/>
-      <c r="H58" s="6">
-        <v>9</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J58" s="6">
-        <v>0.152</v>
-      </c>
-      <c r="K58" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="L58" s="6" t="s">
-        <v>112</v>
-      </c>
+      <c r="D58" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
       <c r="M58" s="6" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="19">
         <v>10</v>
       </c>
-      <c r="B59" s="24" t="s">
+      <c r="B59" s="22" t="s">
         <v>20</v>
       </c>
       <c r="C59" s="21">
         <v>0.65348619560131005</v>
       </c>
-      <c r="D59" s="22"/>
-      <c r="E59" s="23"/>
-      <c r="F59" s="10"/>
-      <c r="H59" s="6">
-        <v>10</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J59" s="6">
-        <v>0.65300000000000002</v>
-      </c>
-      <c r="K59" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="L59" s="6" t="s">
-        <v>115</v>
-      </c>
+      <c r="D59" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
       <c r="M59" s="6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="19">
         <v>11</v>
       </c>
-      <c r="B60" s="24" t="s">
+      <c r="B60" s="22" t="s">
         <v>21</v>
       </c>
       <c r="C60" s="21">
         <v>0.34651380439868901</v>
       </c>
-      <c r="D60" s="22"/>
-      <c r="E60" s="23"/>
-      <c r="F60" s="10"/>
-      <c r="H60" s="6">
-        <v>11</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J60" s="6">
-        <v>0.34699999999999998</v>
-      </c>
-      <c r="K60" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="L60" s="6" t="s">
-        <v>118</v>
-      </c>
+      <c r="D60" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
       <c r="M60" s="6" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3665,58 +4841,50 @@
       <c r="C61" s="21">
         <v>0</v>
       </c>
-      <c r="D61" s="22"/>
-      <c r="E61" s="23"/>
-      <c r="F61" s="10"/>
-      <c r="H61" s="6">
-        <v>12</v>
-      </c>
-      <c r="I61" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J61" s="6">
-        <v>0</v>
-      </c>
-      <c r="K61" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="L61" s="6" t="s">
-        <v>121</v>
-      </c>
+      <c r="D61" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
       <c r="M61" s="6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="19">
         <v>13</v>
       </c>
-      <c r="B62" s="25" t="s">
+      <c r="B62" s="23" t="s">
         <v>23</v>
       </c>
       <c r="C62" s="21">
         <v>0</v>
       </c>
-      <c r="D62" s="22"/>
-      <c r="E62" s="23"/>
-      <c r="F62" s="10"/>
-      <c r="H62" s="6">
-        <v>13</v>
-      </c>
-      <c r="I62" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="J62" s="6">
-        <v>0</v>
-      </c>
-      <c r="K62" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="L62" s="6" t="s">
-        <v>124</v>
-      </c>
+      <c r="D62" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
       <c r="M62" s="6" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3729,58 +4897,50 @@
       <c r="C63" s="21">
         <v>0.34651380439868901</v>
       </c>
-      <c r="D63" s="22"/>
-      <c r="E63" s="23"/>
-      <c r="F63" s="10"/>
-      <c r="H63" s="6">
-        <v>14</v>
-      </c>
-      <c r="I63" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J63" s="6">
-        <v>0.34699999999999998</v>
-      </c>
-      <c r="K63" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="L63" s="6" t="s">
-        <v>127</v>
-      </c>
+      <c r="D63" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
       <c r="M63" s="6" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="19">
         <v>15</v>
       </c>
-      <c r="B64" s="26" t="s">
+      <c r="B64" s="24" t="s">
         <v>25</v>
       </c>
       <c r="C64" s="21">
         <v>3.3156716417910397E-2</v>
       </c>
-      <c r="D64" s="22"/>
-      <c r="E64" s="23"/>
-      <c r="F64" s="10"/>
-      <c r="H64" s="6">
-        <v>15</v>
-      </c>
-      <c r="I64" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J64" s="6">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="K64" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="L64" s="6" t="s">
-        <v>129</v>
-      </c>
+      <c r="D64" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
       <c r="M64" s="6" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3793,58 +4953,50 @@
       <c r="C65" s="21">
         <v>0.13120000000000001</v>
       </c>
-      <c r="D65" s="22"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
-      <c r="H65" s="6">
-        <v>16</v>
-      </c>
-      <c r="I65" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J65" s="6">
-        <v>0.13100000000000001</v>
-      </c>
-      <c r="K65" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="L65" s="6" t="s">
-        <v>132</v>
-      </c>
+      <c r="D65" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
       <c r="M65" s="6" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="19">
         <v>17</v>
       </c>
-      <c r="B66" s="26" t="s">
+      <c r="B66" s="24" t="s">
         <v>27</v>
       </c>
       <c r="C66" s="21">
         <v>0.16435671641791</v>
       </c>
-      <c r="D66" s="22"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="10"/>
-      <c r="H66" s="6">
-        <v>17</v>
-      </c>
-      <c r="I66" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="J66" s="6">
-        <v>0.16400000000000001</v>
-      </c>
-      <c r="K66" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="L66" s="6" t="s">
-        <v>135</v>
-      </c>
+      <c r="D66" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
       <c r="M66" s="6" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3857,29 +5009,32 @@
       <c r="C67" s="21">
         <v>1.9416966917785701</v>
       </c>
-      <c r="D67" s="22"/>
-      <c r="E67" s="10"/>
-      <c r="F67" s="10"/>
-      <c r="H67" s="6">
-        <v>18</v>
-      </c>
-      <c r="I67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J67" s="6">
-        <v>1.9419999999999999</v>
-      </c>
-      <c r="K67" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="L67" s="6" t="s">
-        <v>138</v>
-      </c>
+      <c r="D67" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
       <c r="M67" s="6" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="36.6" customHeight="1" x14ac:dyDescent="0.3"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J68" s="6"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
+      <c r="M68" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
     <row r="69" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="70" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C70" s="3" t="s">
@@ -3922,24 +5077,9 @@
       <c r="F72" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="G72" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="H72" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="I72" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="J72" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="K72" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="L72" s="27" t="s">
-        <v>10</v>
-      </c>
+      <c r="G72" s="25"/>
+      <c r="H72" s="25"/>
+      <c r="I72" s="25"/>
     </row>
     <row r="73" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="19">
@@ -3951,27 +5091,21 @@
       <c r="C73" s="21">
         <v>0.65700000000000003</v>
       </c>
-      <c r="D73" s="22"/>
-      <c r="E73" s="23"/>
-      <c r="F73" s="10"/>
-      <c r="G73" s="6">
-        <v>1</v>
-      </c>
-      <c r="H73" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I73" s="6">
-        <v>0.65700000000000003</v>
-      </c>
-      <c r="J73" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="K73" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="L73" s="6" t="s">
-        <v>142</v>
-      </c>
+      <c r="D73" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6"/>
+      <c r="J73" s="25"/>
+      <c r="K73" s="25"/>
+      <c r="L73" s="25"/>
     </row>
     <row r="74" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="19">
@@ -3983,27 +5117,21 @@
       <c r="C74" s="21">
         <v>7.3319999999999999</v>
       </c>
-      <c r="D74" s="22"/>
-      <c r="E74" s="23"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="6">
-        <v>2</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I74" s="6">
-        <v>7.3319999999999999</v>
-      </c>
-      <c r="J74" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="K74" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="L74" s="6" t="s">
-        <v>82</v>
-      </c>
+      <c r="D74" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
     </row>
     <row r="75" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="19">
@@ -4015,91 +5143,73 @@
       <c r="C75" s="21">
         <v>0.33600000000000002</v>
       </c>
-      <c r="D75" s="22"/>
-      <c r="E75" s="23"/>
-      <c r="F75" s="10"/>
-      <c r="G75" s="6">
-        <v>3</v>
-      </c>
-      <c r="H75" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I75" s="6">
-        <v>0.33600000000000002</v>
-      </c>
-      <c r="J75" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="K75" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L75" s="6" t="s">
-        <v>147</v>
-      </c>
+      <c r="D75" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
+      <c r="I75" s="6"/>
+      <c r="J75" s="6"/>
+      <c r="K75" s="6"/>
+      <c r="L75" s="6"/>
     </row>
     <row r="76" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="19">
         <v>4</v>
       </c>
-      <c r="B76" s="24" t="s">
+      <c r="B76" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C76" s="21">
         <v>0.13856023996000599</v>
       </c>
-      <c r="D76" s="22"/>
-      <c r="E76" s="23"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="6">
-        <v>4</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I76" s="6">
-        <v>0.13900000000000001</v>
-      </c>
-      <c r="J76" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="K76" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="L76" s="6" t="s">
-        <v>150</v>
-      </c>
+      <c r="D76" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
+      <c r="I76" s="6"/>
+      <c r="J76" s="6"/>
+      <c r="K76" s="6"/>
+      <c r="L76" s="6"/>
     </row>
     <row r="77" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="19">
         <v>5</v>
       </c>
-      <c r="B77" s="24" t="s">
+      <c r="B77" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C77" s="21">
         <v>0.82661223129478401</v>
       </c>
-      <c r="D77" s="22"/>
-      <c r="E77" s="23"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="6">
-        <v>5</v>
-      </c>
-      <c r="H77" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I77" s="6">
-        <v>0.82699999999999996</v>
-      </c>
-      <c r="J77" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="K77" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="L77" s="6" t="s">
-        <v>153</v>
-      </c>
+      <c r="D77" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G77" s="6"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="6"/>
+      <c r="J77" s="6"/>
+      <c r="K77" s="6"/>
+      <c r="L77" s="6"/>
     </row>
     <row r="78" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="19">
@@ -4111,187 +5221,151 @@
       <c r="C78" s="21">
         <v>1.7917847025495699</v>
       </c>
-      <c r="D78" s="22"/>
-      <c r="E78" s="23"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="6">
-        <v>6</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I78" s="6">
-        <v>1.792</v>
-      </c>
-      <c r="J78" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="K78" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="L78" s="6" t="s">
-        <v>101</v>
-      </c>
+      <c r="D78" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6"/>
+      <c r="J78" s="6"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
     </row>
     <row r="79" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="19">
         <v>7</v>
       </c>
-      <c r="B79" s="24" t="s">
+      <c r="B79" s="22" t="s">
         <v>17</v>
       </c>
       <c r="C79" s="21">
         <v>7.5237460423262403E-2</v>
       </c>
-      <c r="D79" s="22"/>
-      <c r="E79" s="23"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="6">
-        <v>7</v>
-      </c>
-      <c r="H79" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I79" s="6">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="J79" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="K79" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="L79" s="6" t="s">
-        <v>107</v>
-      </c>
+      <c r="D79" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="6"/>
+      <c r="J79" s="6"/>
+      <c r="K79" s="6"/>
+      <c r="L79" s="6"/>
     </row>
     <row r="80" spans="1:13" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="19">
         <v>8</v>
       </c>
-      <c r="B80" s="24" t="s">
+      <c r="B80" s="22" t="s">
         <v>18</v>
       </c>
       <c r="C80" s="21">
         <v>0.13297783702716201</v>
       </c>
-      <c r="D80" s="22"/>
-      <c r="E80" s="23"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="6">
-        <v>8</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I80" s="6">
-        <v>0.13300000000000001</v>
-      </c>
-      <c r="J80" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="K80" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="L80" s="6" t="s">
-        <v>158</v>
-      </c>
+      <c r="D80" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="G80" s="6"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6"/>
+      <c r="J80" s="6"/>
+      <c r="K80" s="6"/>
+      <c r="L80" s="6"/>
     </row>
     <row r="81" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="19">
         <v>9</v>
       </c>
-      <c r="B81" s="24" t="s">
+      <c r="B81" s="22" t="s">
         <v>19</v>
       </c>
       <c r="C81" s="21">
         <v>0.13297783702716201</v>
       </c>
-      <c r="D81" s="22"/>
-      <c r="E81" s="23"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="6">
-        <v>9</v>
-      </c>
-      <c r="H81" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I81" s="6">
-        <v>0.13300000000000001</v>
-      </c>
-      <c r="J81" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="K81" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="L81" s="6" t="s">
-        <v>160</v>
-      </c>
+      <c r="D81" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F81" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="6"/>
+      <c r="J81" s="6"/>
+      <c r="K81" s="6"/>
+      <c r="L81" s="6"/>
     </row>
     <row r="82" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="19">
         <v>10</v>
       </c>
-      <c r="B82" s="24" t="s">
+      <c r="B82" s="22" t="s">
         <v>20</v>
       </c>
       <c r="C82" s="21">
         <v>0.37337314346960598</v>
       </c>
-      <c r="D82" s="22"/>
-      <c r="E82" s="23"/>
-      <c r="F82" s="10"/>
-      <c r="G82" s="6">
-        <v>10</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I82" s="6">
-        <v>0.373</v>
-      </c>
-      <c r="J82" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="K82" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="L82" s="6" t="s">
-        <v>163</v>
-      </c>
+      <c r="D82" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6"/>
+      <c r="J82" s="6"/>
+      <c r="K82" s="6"/>
+      <c r="L82" s="6"/>
     </row>
     <row r="83" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="19">
         <v>11</v>
       </c>
-      <c r="B83" s="24" t="s">
+      <c r="B83" s="22" t="s">
         <v>21</v>
       </c>
       <c r="C83" s="21">
         <v>0.27530240391976601</v>
       </c>
-      <c r="D83" s="22"/>
-      <c r="E83" s="23"/>
-      <c r="F83" s="10"/>
-      <c r="G83" s="6">
-        <v>11</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="I83" s="6">
-        <v>0.27500000000000002</v>
-      </c>
-      <c r="J83" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="K83" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="L83" s="6" t="s">
-        <v>165</v>
-      </c>
+      <c r="D83" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="6"/>
+      <c r="J83" s="6"/>
+      <c r="K83" s="6"/>
+      <c r="L83" s="6"/>
     </row>
     <row r="84" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="19">
@@ -4303,59 +5377,47 @@
       <c r="C84" s="21">
         <v>0</v>
       </c>
-      <c r="D84" s="22"/>
-      <c r="E84" s="23"/>
-      <c r="F84" s="10"/>
-      <c r="G84" s="6">
-        <v>12</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I84" s="6">
-        <v>0</v>
-      </c>
-      <c r="J84" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="K84" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="L84" s="6" t="s">
-        <v>168</v>
-      </c>
+      <c r="D84" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="6"/>
+      <c r="J84" s="6"/>
+      <c r="K84" s="6"/>
+      <c r="L84" s="6"/>
     </row>
     <row r="85" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="19">
         <v>13</v>
       </c>
-      <c r="B85" s="25" t="s">
+      <c r="B85" s="23" t="s">
         <v>23</v>
       </c>
       <c r="C85" s="21">
         <v>0.351324452610626</v>
       </c>
-      <c r="D85" s="22"/>
-      <c r="E85" s="23"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="6">
-        <v>13</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="I85" s="6">
-        <v>0.35099999999999998</v>
-      </c>
-      <c r="J85" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="K85" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="L85" s="6" t="s">
-        <v>171</v>
-      </c>
+      <c r="D85" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="6"/>
+      <c r="J85" s="6"/>
+      <c r="K85" s="6"/>
+      <c r="L85" s="6"/>
     </row>
     <row r="86" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="19">
@@ -4367,59 +5429,47 @@
       <c r="C86" s="21">
         <v>0.97795130914102002</v>
       </c>
-      <c r="D86" s="22"/>
-      <c r="E86" s="23"/>
-      <c r="F86" s="10"/>
-      <c r="G86" s="6">
-        <v>14</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I86" s="6">
-        <v>0.97799999999999998</v>
-      </c>
-      <c r="J86" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="K86" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="L86" s="6" t="s">
-        <v>104</v>
-      </c>
+      <c r="D86" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G86" s="6"/>
+      <c r="H86" s="6"/>
+      <c r="I86" s="6"/>
+      <c r="J86" s="6"/>
+      <c r="K86" s="6"/>
+      <c r="L86" s="6"/>
     </row>
     <row r="87" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="19">
         <v>15</v>
       </c>
-      <c r="B87" s="26" t="s">
+      <c r="B87" s="24" t="s">
         <v>25</v>
       </c>
       <c r="C87" s="21">
         <v>6.1082089552238802E-2</v>
       </c>
-      <c r="D87" s="22"/>
-      <c r="E87" s="23"/>
-      <c r="F87" s="10"/>
-      <c r="G87" s="6">
-        <v>15</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I87" s="6">
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="J87" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="K87" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="L87" s="6" t="s">
-        <v>176</v>
-      </c>
+      <c r="D87" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G87" s="6"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="6"/>
+      <c r="J87" s="6"/>
+      <c r="K87" s="6"/>
+      <c r="L87" s="6"/>
     </row>
     <row r="88" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="19">
@@ -4431,59 +5481,47 @@
       <c r="C88" s="21">
         <v>0.128711111111111</v>
       </c>
-      <c r="D88" s="22"/>
-      <c r="E88" s="10"/>
-      <c r="F88" s="10"/>
-      <c r="G88" s="6">
-        <v>16</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I88" s="6">
-        <v>0.129</v>
-      </c>
-      <c r="J88" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="K88" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="L88" s="6" t="s">
-        <v>179</v>
-      </c>
+      <c r="D88" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G88" s="6"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="6"/>
+      <c r="J88" s="6"/>
+      <c r="K88" s="6"/>
+      <c r="L88" s="6"/>
     </row>
     <row r="89" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="19">
         <v>17</v>
       </c>
-      <c r="B89" s="26" t="s">
+      <c r="B89" s="24" t="s">
         <v>27</v>
       </c>
       <c r="C89" s="21">
         <v>0.18979320066334901</v>
       </c>
-      <c r="D89" s="22"/>
-      <c r="E89" s="10"/>
-      <c r="F89" s="10"/>
-      <c r="G89" s="6">
-        <v>17</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I89" s="6">
-        <v>0.19</v>
-      </c>
-      <c r="J89" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="K89" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="L89" s="6" t="s">
-        <v>182</v>
-      </c>
+      <c r="D89" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="6"/>
+      <c r="J89" s="6"/>
+      <c r="K89" s="6"/>
+      <c r="L89" s="6"/>
     </row>
     <row r="90" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="15">
@@ -4495,27 +5533,26 @@
       <c r="C90" s="21">
         <v>2.8889074043214999</v>
       </c>
-      <c r="D90" s="22"/>
-      <c r="E90" s="10"/>
-      <c r="F90" s="10"/>
-      <c r="G90" s="6">
-        <v>18</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I90" s="6">
-        <v>2.8889999999999998</v>
-      </c>
-      <c r="J90" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="K90" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="L90" s="6" t="s">
-        <v>184</v>
-      </c>
+      <c r="D90" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="6"/>
+      <c r="J90" s="6"/>
+      <c r="K90" s="6"/>
+      <c r="L90" s="6"/>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="J91" s="6"/>
+      <c r="K91" s="6"/>
+      <c r="L91" s="6"/>
     </row>
     <row r="92" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="93" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4559,24 +5596,9 @@
       <c r="F95" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="G95" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="H95" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="I95" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="J95" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="K95" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="L95" s="27" t="s">
-        <v>10</v>
-      </c>
+      <c r="G95" s="25"/>
+      <c r="H95" s="25"/>
+      <c r="I95" s="25"/>
     </row>
     <row r="96" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="19">
@@ -4588,27 +5610,21 @@
       <c r="C96" s="21">
         <v>0.82099999999999995</v>
       </c>
-      <c r="D96" s="22"/>
-      <c r="E96" s="23"/>
-      <c r="F96" s="10"/>
-      <c r="G96" s="6">
-        <v>1</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I96" s="6">
-        <v>0.82099999999999995</v>
-      </c>
-      <c r="J96" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="K96" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="L96" s="6" t="s">
-        <v>187</v>
-      </c>
+      <c r="D96" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G96" s="6"/>
+      <c r="H96" s="6"/>
+      <c r="I96" s="6"/>
+      <c r="J96" s="25"/>
+      <c r="K96" s="25"/>
+      <c r="L96" s="25"/>
     </row>
     <row r="97" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="19">
@@ -4620,27 +5636,21 @@
       <c r="C97" s="21">
         <v>9.0020000000000007</v>
       </c>
-      <c r="D97" s="22"/>
-      <c r="E97" s="23"/>
-      <c r="F97" s="10"/>
-      <c r="G97" s="6">
-        <v>2</v>
-      </c>
-      <c r="H97" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I97" s="6">
-        <v>9.0020000000000007</v>
-      </c>
-      <c r="J97" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="K97" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="L97" s="6" t="s">
-        <v>190</v>
-      </c>
+      <c r="D97" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="G97" s="6"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="6"/>
+      <c r="J97" s="6"/>
+      <c r="K97" s="6"/>
+      <c r="L97" s="6"/>
     </row>
     <row r="98" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="19">
@@ -4652,91 +5662,73 @@
       <c r="C98" s="21">
         <v>0.19400000000000001</v>
       </c>
-      <c r="D98" s="22"/>
-      <c r="E98" s="23"/>
-      <c r="F98" s="10"/>
-      <c r="G98" s="6">
-        <v>3</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I98" s="6">
-        <v>0.19400000000000001</v>
-      </c>
-      <c r="J98" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="K98" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="L98" s="6" t="s">
-        <v>193</v>
-      </c>
+      <c r="D98" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6"/>
+      <c r="J98" s="6"/>
+      <c r="K98" s="6"/>
+      <c r="L98" s="6"/>
     </row>
     <row r="99" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="19">
         <v>4</v>
       </c>
-      <c r="B99" s="24" t="s">
+      <c r="B99" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C99" s="21">
         <v>0.109410801963993</v>
       </c>
-      <c r="D99" s="22"/>
-      <c r="E99" s="23"/>
-      <c r="F99" s="10"/>
-      <c r="G99" s="6">
-        <v>4</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I99" s="6">
-        <v>0.109</v>
-      </c>
-      <c r="J99" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="K99" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="L99" s="6" t="s">
-        <v>195</v>
-      </c>
+      <c r="D99" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="G99" s="6"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="6"/>
+      <c r="J99" s="6"/>
+      <c r="K99" s="6"/>
+      <c r="L99" s="6"/>
     </row>
     <row r="100" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="19">
         <v>5</v>
       </c>
-      <c r="B100" s="24" t="s">
+      <c r="B100" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C100" s="21">
         <v>0.87283142389525303</v>
       </c>
-      <c r="D100" s="22"/>
-      <c r="E100" s="23"/>
-      <c r="F100" s="10"/>
-      <c r="G100" s="6">
-        <v>5</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I100" s="6">
-        <v>0.873</v>
-      </c>
-      <c r="J100" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="K100" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="L100" s="6" t="s">
-        <v>198</v>
-      </c>
+      <c r="D100" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G100" s="6"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="6"/>
+      <c r="J100" s="6"/>
+      <c r="K100" s="6"/>
+      <c r="L100" s="6"/>
     </row>
     <row r="101" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="19">
@@ -4748,187 +5740,151 @@
       <c r="C101" s="21">
         <v>1.8550736497545</v>
       </c>
-      <c r="D101" s="22"/>
-      <c r="E101" s="23"/>
-      <c r="F101" s="10"/>
-      <c r="G101" s="6">
-        <v>6</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I101" s="6">
-        <v>1.855</v>
-      </c>
-      <c r="J101" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="K101" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="L101" s="6" t="s">
-        <v>201</v>
-      </c>
+      <c r="D101" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="G101" s="6"/>
+      <c r="H101" s="6"/>
+      <c r="I101" s="6"/>
+      <c r="J101" s="6"/>
+      <c r="K101" s="6"/>
+      <c r="L101" s="6"/>
     </row>
     <row r="102" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="19">
         <v>7</v>
       </c>
-      <c r="B102" s="24" t="s">
+      <c r="B102" s="22" t="s">
         <v>17</v>
       </c>
       <c r="C102" s="21">
         <v>6.1211129296235497E-2</v>
       </c>
-      <c r="D102" s="22"/>
-      <c r="E102" s="23"/>
-      <c r="F102" s="10"/>
-      <c r="G102" s="6">
-        <v>7</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I102" s="6">
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="J102" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="K102" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="L102" s="6" t="s">
-        <v>204</v>
-      </c>
+      <c r="D102" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="G102" s="6"/>
+      <c r="H102" s="6"/>
+      <c r="I102" s="6"/>
+      <c r="J102" s="6"/>
+      <c r="K102" s="6"/>
+      <c r="L102" s="6"/>
     </row>
     <row r="103" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="19">
         <v>8</v>
       </c>
-      <c r="B103" s="24" t="s">
+      <c r="B103" s="22" t="s">
         <v>18</v>
       </c>
       <c r="C103" s="21">
         <v>8.3715220949263397E-2</v>
       </c>
-      <c r="D103" s="22"/>
-      <c r="E103" s="23"/>
-      <c r="F103" s="10"/>
-      <c r="G103" s="6">
-        <v>8</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I103" s="6">
-        <v>8.4000000000000005E-2</v>
-      </c>
-      <c r="J103" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="K103" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="L103" s="6" t="s">
-        <v>75</v>
-      </c>
+      <c r="D103" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G103" s="6"/>
+      <c r="H103" s="6"/>
+      <c r="I103" s="6"/>
+      <c r="J103" s="6"/>
+      <c r="K103" s="6"/>
+      <c r="L103" s="6"/>
     </row>
     <row r="104" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="19">
         <v>9</v>
       </c>
-      <c r="B104" s="24" t="s">
+      <c r="B104" s="22" t="s">
         <v>19</v>
       </c>
       <c r="C104" s="21">
         <v>8.3715220949263397E-2</v>
       </c>
-      <c r="D104" s="22"/>
-      <c r="E104" s="23"/>
-      <c r="F104" s="10"/>
-      <c r="G104" s="6">
-        <v>9</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I104" s="6">
-        <v>8.4000000000000005E-2</v>
-      </c>
-      <c r="J104" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="K104" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="L104" s="6" t="s">
-        <v>104</v>
-      </c>
+      <c r="D104" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G104" s="6"/>
+      <c r="H104" s="6"/>
+      <c r="I104" s="6"/>
+      <c r="J104" s="6"/>
+      <c r="K104" s="6"/>
+      <c r="L104" s="6"/>
     </row>
     <row r="105" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="19">
         <v>10</v>
       </c>
-      <c r="B105" s="24" t="s">
+      <c r="B105" s="22" t="s">
         <v>20</v>
       </c>
       <c r="C105" s="21">
         <v>0.30808002481389501</v>
       </c>
-      <c r="D105" s="22"/>
-      <c r="E105" s="23"/>
-      <c r="F105" s="10"/>
-      <c r="G105" s="6">
-        <v>10</v>
-      </c>
-      <c r="H105" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I105" s="6">
-        <v>0.308</v>
-      </c>
-      <c r="J105" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="K105" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="L105" s="6" t="s">
-        <v>210</v>
-      </c>
+      <c r="D105" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="G105" s="6"/>
+      <c r="H105" s="6"/>
+      <c r="I105" s="6"/>
+      <c r="J105" s="6"/>
+      <c r="K105" s="6"/>
+      <c r="L105" s="6"/>
     </row>
     <row r="106" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="19">
         <v>11</v>
       </c>
-      <c r="B106" s="24" t="s">
+      <c r="B106" s="22" t="s">
         <v>21</v>
       </c>
       <c r="C106" s="21">
         <v>0.21789702233250599</v>
       </c>
-      <c r="D106" s="22"/>
-      <c r="E106" s="23"/>
-      <c r="F106" s="10"/>
-      <c r="G106" s="6">
-        <v>11</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="I106" s="6">
-        <v>0.218</v>
-      </c>
-      <c r="J106" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="K106" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="L106" s="6" t="s">
-        <v>213</v>
-      </c>
+      <c r="D106" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E106" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="G106" s="6"/>
+      <c r="H106" s="6"/>
+      <c r="I106" s="6"/>
+      <c r="J106" s="6"/>
+      <c r="K106" s="6"/>
+      <c r="L106" s="6"/>
     </row>
     <row r="107" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="19">
@@ -4940,59 +5896,47 @@
       <c r="C107" s="21">
         <v>0.249379652605459</v>
       </c>
-      <c r="D107" s="22"/>
-      <c r="E107" s="23"/>
-      <c r="F107" s="10"/>
-      <c r="G107" s="6">
-        <v>12</v>
-      </c>
-      <c r="H107" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I107" s="6">
-        <v>0.249</v>
-      </c>
-      <c r="J107" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="K107" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="L107" s="6" t="s">
-        <v>216</v>
-      </c>
+      <c r="D107" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="G107" s="6"/>
+      <c r="H107" s="6"/>
+      <c r="I107" s="6"/>
+      <c r="J107" s="6"/>
+      <c r="K107" s="6"/>
+      <c r="L107" s="6"/>
     </row>
     <row r="108" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="19">
         <v>13</v>
       </c>
-      <c r="B108" s="25" t="s">
+      <c r="B108" s="23" t="s">
         <v>23</v>
       </c>
       <c r="C108" s="21">
         <v>0.224643300248138</v>
       </c>
-      <c r="D108" s="22"/>
-      <c r="E108" s="23"/>
-      <c r="F108" s="10"/>
-      <c r="G108" s="6">
-        <v>13</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="I108" s="6">
-        <v>0.22500000000000001</v>
-      </c>
-      <c r="J108" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="K108" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="L108" s="6" t="s">
-        <v>218</v>
-      </c>
+      <c r="D108" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G108" s="6"/>
+      <c r="H108" s="6"/>
+      <c r="I108" s="6"/>
+      <c r="J108" s="6"/>
+      <c r="K108" s="6"/>
+      <c r="L108" s="6"/>
     </row>
     <row r="109" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="19">
@@ -5004,59 +5948,47 @@
       <c r="C109" s="21">
         <v>1.3905862282878401</v>
       </c>
-      <c r="D109" s="22"/>
-      <c r="E109" s="23"/>
-      <c r="F109" s="10"/>
-      <c r="G109" s="6">
-        <v>14</v>
-      </c>
-      <c r="H109" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I109" s="6">
-        <v>1.391</v>
-      </c>
-      <c r="J109" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="K109" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="L109" s="6" t="s">
-        <v>104</v>
-      </c>
+      <c r="D109" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G109" s="6"/>
+      <c r="H109" s="6"/>
+      <c r="I109" s="6"/>
+      <c r="J109" s="6"/>
+      <c r="K109" s="6"/>
+      <c r="L109" s="6"/>
     </row>
     <row r="110" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="19">
         <v>15</v>
       </c>
-      <c r="B110" s="26" t="s">
+      <c r="B110" s="24" t="s">
         <v>25</v>
       </c>
       <c r="C110" s="21">
         <v>6.6589552238805902E-2</v>
       </c>
-      <c r="D110" s="22"/>
-      <c r="E110" s="23"/>
-      <c r="F110" s="10"/>
-      <c r="G110" s="6">
-        <v>15</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I110" s="6">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="J110" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="K110" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="L110" s="6" t="s">
-        <v>176</v>
-      </c>
+      <c r="D110" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G110" s="6"/>
+      <c r="H110" s="6"/>
+      <c r="I110" s="6"/>
+      <c r="J110" s="6"/>
+      <c r="K110" s="6"/>
+      <c r="L110" s="6"/>
     </row>
     <row r="111" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="19">
@@ -5068,59 +6000,47 @@
       <c r="C111" s="21">
         <v>0.109118181818181</v>
       </c>
-      <c r="D111" s="22"/>
-      <c r="E111" s="10"/>
-      <c r="F111" s="10"/>
-      <c r="G111" s="6">
-        <v>16</v>
-      </c>
-      <c r="H111" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I111" s="6">
-        <v>0.109</v>
-      </c>
-      <c r="J111" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="K111" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="L111" s="6" t="s">
-        <v>179</v>
-      </c>
+      <c r="D111" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G111" s="6"/>
+      <c r="H111" s="6"/>
+      <c r="I111" s="6"/>
+      <c r="J111" s="6"/>
+      <c r="K111" s="6"/>
+      <c r="L111" s="6"/>
     </row>
     <row r="112" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="19">
         <v>17</v>
       </c>
-      <c r="B112" s="26" t="s">
+      <c r="B112" s="24" t="s">
         <v>27</v>
       </c>
       <c r="C112" s="21">
         <v>0.175707734056987</v>
       </c>
-      <c r="D112" s="22"/>
-      <c r="E112" s="10"/>
-      <c r="F112" s="10"/>
-      <c r="G112" s="6">
-        <v>17</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I112" s="6">
-        <v>0.17599999999999999</v>
-      </c>
-      <c r="J112" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="K112" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="L112" s="6" t="s">
-        <v>182</v>
-      </c>
+      <c r="D112" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E112" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="G112" s="6"/>
+      <c r="H112" s="6"/>
+      <c r="I112" s="6"/>
+      <c r="J112" s="6"/>
+      <c r="K112" s="6"/>
+      <c r="L112" s="6"/>
     </row>
     <row r="113" spans="1:12" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="15">
@@ -5132,44 +6052,509 @@
       <c r="C113" s="21">
         <v>3.2820512820512802</v>
       </c>
-      <c r="D113" s="22"/>
-      <c r="E113" s="10"/>
-      <c r="F113" s="10"/>
-      <c r="G113" s="6">
-        <v>18</v>
-      </c>
-      <c r="H113" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I113" s="6">
-        <v>3.282</v>
-      </c>
-      <c r="J113" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="K113" s="6" t="s">
+      <c r="D113" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E113" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="F113" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="G113" s="6"/>
+      <c r="H113" s="6"/>
+      <c r="I113" s="6"/>
+      <c r="J113" s="6"/>
+      <c r="K113" s="6"/>
+      <c r="L113" s="6"/>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="J114" s="6"/>
+      <c r="K114" s="6"/>
+      <c r="L114" s="6"/>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E115" s="26" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E117" s="26" t="s">
         <v>222</v>
       </c>
-      <c r="L113" s="6" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E115" s="28" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E117" s="28" t="s">
-        <v>225</v>
-      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C22:F23"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C00785CA-40B3-4F36-8E16-460E90353309}">
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0</v>
+      </c>
+      <c r="E1">
+        <v>0</v>
+      </c>
+      <c r="F1">
+        <v>0</v>
+      </c>
+      <c r="G1">
+        <v>0</v>
+      </c>
+      <c r="H1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>0.1</v>
+      </c>
+      <c r="F2">
+        <f>D2/$D$12</f>
+        <v>0.01</v>
+      </c>
+      <c r="G2">
+        <f>SUM($F$2:F2)</f>
+        <v>0.01</v>
+      </c>
+      <c r="H2">
+        <f>SUM($E$2:E2)</f>
+        <v>0.1</v>
+      </c>
+      <c r="I2">
+        <f>H2-G2</f>
+        <v>9.0000000000000011E-2</v>
+      </c>
+      <c r="J2">
+        <f>I2*$E$2</f>
+        <v>9.0000000000000011E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>20</v>
+      </c>
+      <c r="C3">
+        <v>0.9</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>0.1</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F12" si="0">D3/$D$12</f>
+        <v>0.02</v>
+      </c>
+      <c r="G3">
+        <f>SUM($F$2:F3)</f>
+        <v>0.03</v>
+      </c>
+      <c r="H3">
+        <f>SUM($E$2:E3)</f>
+        <v>0.2</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I11" si="1">H3-G3</f>
+        <v>0.17</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J11" si="2">I3*$E$2</f>
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>30</v>
+      </c>
+      <c r="C4">
+        <v>0.8</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>0.1</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>0.03</v>
+      </c>
+      <c r="G4">
+        <f>SUM($F$2:F4)</f>
+        <v>0.06</v>
+      </c>
+      <c r="H4">
+        <f>SUM($E$2:E4)</f>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="1"/>
+        <v>0.24000000000000005</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="2"/>
+        <v>2.4000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>40</v>
+      </c>
+      <c r="C5">
+        <v>0.7</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>0.1</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>0.04</v>
+      </c>
+      <c r="G5">
+        <f>SUM($F$2:F5)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H5">
+        <f>SUM($E$2:E5)</f>
+        <v>0.4</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="1"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="2"/>
+        <v>3.0000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>50</v>
+      </c>
+      <c r="C6">
+        <v>0.6</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>0.1</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="G6">
+        <f>SUM($F$2:F6)</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="H6">
+        <f>SUM($E$2:E6)</f>
+        <v>0.5</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="2"/>
+        <v>3.4999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>60</v>
+      </c>
+      <c r="C7">
+        <v>0.5</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>0.1</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="G7">
+        <f>SUM($F$2:F7)</f>
+        <v>0.25</v>
+      </c>
+      <c r="H7">
+        <f>SUM($E$2:E7)</f>
+        <v>0.6</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="2"/>
+        <v>3.4999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>70</v>
+      </c>
+      <c r="C8">
+        <v>0.4</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>0.1</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="G8">
+        <f>SUM($F$2:F8)</f>
+        <v>0.35</v>
+      </c>
+      <c r="H8">
+        <f>SUM($E$2:E8)</f>
+        <v>0.7</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="2"/>
+        <v>3.4999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>80</v>
+      </c>
+      <c r="C9">
+        <v>0.3</v>
+      </c>
+      <c r="D9">
+        <v>15</v>
+      </c>
+      <c r="E9">
+        <v>0.1</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>0.15</v>
+      </c>
+      <c r="G9">
+        <f>SUM($F$2:F9)</f>
+        <v>0.5</v>
+      </c>
+      <c r="H9">
+        <f>SUM($E$2:E9)</f>
+        <v>0.79999999999999993</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="1"/>
+        <v>0.29999999999999993</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="2"/>
+        <v>2.9999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>90</v>
+      </c>
+      <c r="C10">
+        <v>0.2</v>
+      </c>
+      <c r="D10">
+        <v>20</v>
+      </c>
+      <c r="E10">
+        <v>0.1</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="G10">
+        <f>SUM($F$2:F10)</f>
+        <v>0.7</v>
+      </c>
+      <c r="H10">
+        <f>SUM($E$2:E10)</f>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="1"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="2"/>
+        <v>1.9999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>100</v>
+      </c>
+      <c r="C11">
+        <v>0.1</v>
+      </c>
+      <c r="D11">
+        <v>30</v>
+      </c>
+      <c r="E11">
+        <v>0.1</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+      <c r="G11">
+        <f>SUM($F$2:F11)</f>
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <f>SUM($E$2:E11)</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <f t="shared" ref="B12:C12" si="3">SUM(B2:B11)</f>
+        <v>550</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="3"/>
+        <v>5.5</v>
+      </c>
+      <c r="D12">
+        <f>SUM(D2:D11)</f>
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <f>SUM(E2:E11)</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <f>SUM(J2:J11)</f>
+        <v>0.23500000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H14" t="s">
+        <v>341</v>
+      </c>
+      <c r="I14">
+        <f>J12*0.1/0.5</f>
+        <v>4.7000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H15" t="s">
+        <v>342</v>
+      </c>
+      <c r="I15">
+        <f>F6*100</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H16" t="s">
+        <v>343</v>
+      </c>
+      <c r="I16">
+        <f>D12/A11</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H17" t="s">
+        <v>344</v>
+      </c>
+      <c r="I17">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D001B0C2-4A4D-431A-8C0C-16DB39E3151B}">
   <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5181,401 +6566,401 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="D1" s="28" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="E1" s="28" t="s">
         <v>227</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="F1" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="G1" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+    </row>
+    <row r="2" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="29" t="s">
         <v>229</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="B2" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="C2" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="D2" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="30"/>
+      <c r="B3" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>274</v>
+      </c>
+      <c r="K3" s="6"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="30"/>
+      <c r="B4" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="G4" s="30" t="s">
         <v>275</v>
       </c>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-    </row>
-    <row r="2" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="K4" s="6"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="30"/>
+      <c r="B5" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="D5" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="E5" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="K5" s="6"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="29" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>244</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="G6" s="30" t="s">
+        <v>277</v>
+      </c>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="6"/>
+    </row>
+    <row r="7" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="30"/>
+      <c r="B7" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="E7" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="F7" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>278</v>
+      </c>
+      <c r="K7" s="6"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>279</v>
+      </c>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="6"/>
+    </row>
+    <row r="9" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="30"/>
+      <c r="B9" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="K9" s="6"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="6"/>
+    </row>
+    <row r="10" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="30"/>
+      <c r="B10" s="29" t="s">
+        <v>255</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="F10" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="D2" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="E2" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="F2" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="G2" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="6"/>
-    </row>
-    <row r="3" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32"/>
-      <c r="B3" s="31" t="s">
-        <v>238</v>
-      </c>
-      <c r="C3" s="32" t="s">
-        <v>239</v>
-      </c>
-      <c r="D3" s="32" t="s">
+      <c r="G10" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="K10" s="6"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="6"/>
+    </row>
+    <row r="11" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="29" t="s">
+        <v>257</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="G11" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="6"/>
+    </row>
+    <row r="12" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="30"/>
+      <c r="B12" s="29" t="s">
+        <v>260</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="K12" s="6"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="6"/>
+    </row>
+    <row r="13" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="29" t="s">
+        <v>262</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>263</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="G13" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="6"/>
+    </row>
+    <row r="14" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="30"/>
+      <c r="B14" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="G14" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="K14" s="6"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="6"/>
+    </row>
+    <row r="15" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="29" t="s">
+        <v>267</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>268</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="E15" s="30" t="s">
         <v>240</v>
       </c>
-      <c r="E3" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="F3" s="32" t="s">
-        <v>240</v>
-      </c>
-      <c r="G3" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="6"/>
-    </row>
-    <row r="4" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="32"/>
-      <c r="B4" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>242</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="F4" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="G4" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="6"/>
-    </row>
-    <row r="5" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="32"/>
-      <c r="B5" s="31" t="s">
-        <v>244</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="E5" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="F5" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="G5" s="32" t="s">
-        <v>279</v>
-      </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="6"/>
-    </row>
-    <row r="6" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>247</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>248</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>249</v>
-      </c>
-      <c r="E6" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="F6" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="G6" s="32" t="s">
-        <v>280</v>
-      </c>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="6"/>
-    </row>
-    <row r="7" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="32"/>
-      <c r="B7" s="31" t="s">
-        <v>250</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>251</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>249</v>
-      </c>
-      <c r="E7" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="F7" s="32" t="s">
-        <v>249</v>
-      </c>
-      <c r="G7" s="32" t="s">
-        <v>281</v>
-      </c>
-      <c r="K7" s="6"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="6"/>
-    </row>
-    <row r="8" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="31" t="s">
-        <v>252</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>253</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>254</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>249</v>
-      </c>
-      <c r="E8" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="F8" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="G8" s="32" t="s">
-        <v>282</v>
-      </c>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="6"/>
-    </row>
-    <row r="9" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="32"/>
-      <c r="B9" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>256</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>257</v>
-      </c>
-      <c r="E9" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="F9" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="G9" s="32" t="s">
-        <v>283</v>
-      </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="6"/>
-    </row>
-    <row r="10" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="32"/>
-      <c r="B10" s="31" t="s">
-        <v>258</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>259</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>249</v>
-      </c>
-      <c r="E10" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="F10" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="G10" s="32" t="s">
-        <v>284</v>
-      </c>
-      <c r="K10" s="6"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="6"/>
-    </row>
-    <row r="11" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="31" t="s">
-        <v>260</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>261</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>262</v>
-      </c>
-      <c r="D11" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="E11" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="F11" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="G11" s="32" t="s">
-        <v>285</v>
-      </c>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="6"/>
-    </row>
-    <row r="12" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="32"/>
-      <c r="B12" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="E12" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="F12" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="G12" s="32" t="s">
+      <c r="F15" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="G15" s="30" t="s">
         <v>286</v>
       </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="6"/>
-    </row>
-    <row r="13" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="31" t="s">
-        <v>265</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>266</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>267</v>
-      </c>
-      <c r="D13" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="E13" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="F13" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="G13" s="32" t="s">
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="6"/>
+    </row>
+    <row r="16" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="30"/>
+      <c r="B16" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="G16" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="6"/>
-    </row>
-    <row r="14" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="32"/>
-      <c r="B14" s="31" t="s">
-        <v>268</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>269</v>
-      </c>
-      <c r="D14" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="E14" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="F14" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="G14" s="32" t="s">
-        <v>288</v>
-      </c>
-      <c r="K14" s="6"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="6"/>
-    </row>
-    <row r="15" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="31" t="s">
-        <v>270</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>271</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="E15" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="F15" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="G15" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="6"/>
-    </row>
-    <row r="16" spans="1:13" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="32"/>
-      <c r="B16" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>274</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="E16" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="F16" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="G16" s="32" t="s">
-        <v>290</v>
-      </c>
       <c r="K16" s="6"/>
-      <c r="L16" s="29"/>
+      <c r="L16" s="27"/>
       <c r="M16" s="6"/>
     </row>
   </sheetData>
@@ -5583,330 +6968,355 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18BF3D88-B717-4890-94D1-1DEE25C51264}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:13" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>288</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1" s="55"/>
+      <c r="D1" s="54" t="s">
+        <v>290</v>
+      </c>
+      <c r="E1" s="55"/>
+      <c r="F1" s="51" t="s">
         <v>291</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="G1" s="51" t="s">
         <v>292</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="50" t="s">
+      <c r="H1" s="6"/>
+      <c r="J1">
+        <v>4</v>
+      </c>
+      <c r="K1">
+        <v>1</v>
+      </c>
+      <c r="L1">
+        <f>4.75+0.15</f>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="M1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="52"/>
+      <c r="B2" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="E1" s="51"/>
-      <c r="F1" s="47" t="s">
+      <c r="C2" s="58" t="s">
         <v>294</v>
       </c>
-      <c r="G1" s="47" t="s">
+      <c r="D2" s="56" t="s">
         <v>295</v>
       </c>
-      <c r="H1" s="6"/>
-    </row>
-    <row r="2" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="48"/>
-      <c r="B2" s="52" t="s">
+      <c r="E2" s="58" t="s">
         <v>296</v>
       </c>
-      <c r="C2" s="54" t="s">
-        <v>297</v>
-      </c>
-      <c r="D2" s="52" t="s">
-        <v>298</v>
-      </c>
-      <c r="E2" s="54" t="s">
-        <v>299</v>
-      </c>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
       <c r="H2" s="6"/>
-    </row>
-    <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="49"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="53"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
     </row>
-    <row r="4" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="56" t="s">
-        <v>300</v>
-      </c>
-      <c r="B4" s="33">
+    <row r="4" spans="1:13" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="61" t="s">
+        <v>297</v>
+      </c>
+      <c r="B4" s="31">
         <v>32768</v>
       </c>
-      <c r="C4" s="57" t="s">
-        <v>301</v>
-      </c>
-      <c r="D4" s="36">
+      <c r="C4" s="63" t="s">
+        <v>298</v>
+      </c>
+      <c r="D4" s="34">
         <v>128</v>
       </c>
-      <c r="E4" s="37">
+      <c r="E4" s="35">
         <v>4</v>
       </c>
-      <c r="F4" s="38">
+      <c r="F4" s="36">
         <v>4</v>
       </c>
-      <c r="G4" s="38">
+      <c r="G4" s="36">
         <v>0</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="48"/>
-      <c r="B5" s="33">
+    <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="52"/>
+      <c r="B5" s="31">
         <v>-4097</v>
       </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="36">
+      <c r="C5" s="64"/>
+      <c r="D5" s="34">
         <v>128</v>
       </c>
-      <c r="E5" s="37">
+      <c r="E5" s="35">
         <v>5</v>
       </c>
-      <c r="F5" s="38">
+      <c r="F5" s="36">
         <v>2</v>
       </c>
-      <c r="G5" s="38">
+      <c r="G5" s="36">
         <v>0</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
     </row>
-    <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="48"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="36">
+    <row r="6" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="52"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="34">
         <v>128</v>
       </c>
-      <c r="E6" s="37">
+      <c r="E6" s="35">
         <v>6</v>
       </c>
-      <c r="F6" s="38">
+      <c r="F6" s="36">
         <v>2</v>
       </c>
-      <c r="G6" s="38">
+      <c r="G6" s="36">
         <v>0</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
     </row>
-    <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="48"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="36">
+    <row r="7" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="52"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="34">
         <v>128</v>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="35">
         <v>7</v>
       </c>
-      <c r="F7" s="38">
+      <c r="F7" s="36">
         <v>2</v>
       </c>
-      <c r="G7" s="38">
+      <c r="G7" s="36">
         <v>0</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
     </row>
-    <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="49"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="39">
+    <row r="8" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="53"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="37">
         <v>128</v>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="38">
         <v>8</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="39">
         <v>2</v>
       </c>
-      <c r="G8" s="41">
+      <c r="G8" s="39">
         <v>0</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="56">
+    <row r="9" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="61">
         <v>3</v>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="31">
         <v>32769</v>
       </c>
-      <c r="C9" s="57" t="s">
-        <v>302</v>
-      </c>
-      <c r="D9" s="52">
+      <c r="C9" s="63" t="s">
+        <v>299</v>
+      </c>
+      <c r="D9" s="56">
         <v>128</v>
       </c>
-      <c r="E9" s="69">
+      <c r="E9" s="67">
         <v>4</v>
       </c>
-      <c r="F9" s="60">
+      <c r="F9" s="71">
         <v>2</v>
       </c>
-      <c r="G9" s="60" t="s">
-        <v>303</v>
-      </c>
-      <c r="H9" s="63"/>
-      <c r="I9" s="62"/>
-    </row>
-    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="49"/>
-      <c r="B10" s="42">
+      <c r="G9" s="71" t="s">
+        <v>300</v>
+      </c>
+      <c r="H9" s="73"/>
+      <c r="I9" s="60"/>
+    </row>
+    <row r="10" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="53"/>
+      <c r="B10" s="40">
         <v>-8193</v>
       </c>
-      <c r="C10" s="55"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="62"/>
-    </row>
-    <row r="11" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="56">
+      <c r="C10" s="59"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="60"/>
+    </row>
+    <row r="11" spans="1:13" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="61">
         <v>4</v>
       </c>
-      <c r="B11" s="33">
+      <c r="B11" s="31">
         <v>32770</v>
       </c>
-      <c r="C11" s="57" t="s">
-        <v>304</v>
-      </c>
-      <c r="D11" s="36">
+      <c r="C11" s="63" t="s">
+        <v>301</v>
+      </c>
+      <c r="D11" s="34">
         <v>128</v>
       </c>
-      <c r="E11" s="44">
+      <c r="E11" s="42">
         <v>1</v>
       </c>
-      <c r="F11" s="38">
+      <c r="F11" s="36">
         <v>2</v>
       </c>
-      <c r="G11" s="38" t="s">
-        <v>303</v>
+      <c r="G11" s="36" t="s">
+        <v>300</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
     </row>
-    <row r="12" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="48"/>
-      <c r="B12" s="33">
+    <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="52"/>
+      <c r="B12" s="31">
         <v>-12289</v>
       </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="36">
+      <c r="C12" s="64"/>
+      <c r="D12" s="34">
         <v>128</v>
       </c>
-      <c r="E12" s="68">
+      <c r="E12" s="45">
         <v>2</v>
       </c>
-      <c r="F12" s="38">
+      <c r="F12" s="36">
         <v>4</v>
       </c>
-      <c r="G12" s="38" t="s">
-        <v>305</v>
+      <c r="G12" s="36" t="s">
+        <v>302</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
     </row>
-    <row r="13" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="48"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="45"/>
+    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="52"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="43"/>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="64"/>
-      <c r="B14" s="43"/>
+    <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="62"/>
+      <c r="B14" s="41"/>
       <c r="C14" s="65"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="45"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="43"/>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="66">
+    <row r="15" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="69">
         <v>5</v>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="31">
         <v>32771</v>
       </c>
-      <c r="C15" s="67" t="s">
-        <v>306</v>
-      </c>
-      <c r="D15" s="36">
+      <c r="C15" s="70" t="s">
+        <v>303</v>
+      </c>
+      <c r="D15" s="34">
         <v>128</v>
       </c>
-      <c r="E15" s="46">
+      <c r="E15" s="44">
         <v>4</v>
       </c>
-      <c r="F15" s="38">
+      <c r="F15" s="36">
         <v>4</v>
       </c>
-      <c r="G15" s="38" t="s">
-        <v>305</v>
+      <c r="G15" s="36" t="s">
+        <v>302</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="48"/>
-      <c r="B16" s="33">
+    <row r="16" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="52"/>
+      <c r="B16" s="31">
         <v>-16385</v>
       </c>
-      <c r="C16" s="58"/>
-      <c r="D16" s="36">
+      <c r="C16" s="64"/>
+      <c r="D16" s="34">
         <v>128</v>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="42">
         <v>7</v>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="36">
         <v>2</v>
       </c>
-      <c r="G16" s="38" t="s">
-        <v>303</v>
+      <c r="G16" s="36" t="s">
+        <v>300</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
     </row>
     <row r="17" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="64"/>
-      <c r="B17" s="43"/>
+      <c r="A17" s="62"/>
+      <c r="B17" s="41"/>
       <c r="C17" s="65"/>
-      <c r="D17" s="36">
+      <c r="D17" s="34">
         <v>128</v>
       </c>
-      <c r="E17" s="46">
+      <c r="E17" s="44">
         <v>8</v>
       </c>
-      <c r="F17" s="38">
+      <c r="F17" s="36">
         <v>4</v>
       </c>
-      <c r="G17" s="38" t="s">
-        <v>307</v>
+      <c r="G17" s="36" t="s">
+        <v>304</v>
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
